--- a/importacaoV6.xlsx
+++ b/importacaoV6.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="66">
   <si>
     <t>Parametros Gerais</t>
   </si>
@@ -216,6 +216,12 @@
   </si>
   <si>
     <t>sim | true | 1</t>
+  </si>
+  <si>
+    <t>FIM MANUAL</t>
+  </si>
+  <si>
+    <t>IFVF</t>
   </si>
 </sst>
 </file>
@@ -2690,11 +2696,19 @@
       <c r="AV22" s="50"/>
     </row>
     <row r="23" spans="1:48" x14ac:dyDescent="0.3">
-      <c r="A23" s="37"/>
-      <c r="B23" s="3"/>
+      <c r="A23" s="37">
+        <v>4</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>64</v>
+      </c>
       <c r="C23" s="3"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="31"/>
+      <c r="D23" s="30">
+        <v>4</v>
+      </c>
+      <c r="E23" s="31" t="s">
+        <v>65</v>
+      </c>
       <c r="F23" s="21"/>
       <c r="G23" s="18"/>
       <c r="H23" s="25">
